--- a/artfynd/S 1000-2026 artfynd.xlsx
+++ b/artfynd/S 1000-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133115044</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120410327</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120051538</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133114883</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1230,6 +1255,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133114909</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,6 +1370,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95828689</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1464,6 +1499,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120410077</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1584,6 +1624,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120410201</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1690,6 +1735,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133114940</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1818,6 +1868,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819433</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1946,6 +2001,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121737051</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2074,6 +2134,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130778709</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2204,6 +2269,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111452858</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2346,6 +2416,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115561300</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2480,6 +2555,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115655325</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2614,6 +2694,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117491947</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2744,6 +2829,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117947730</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2864,6 +2954,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120030509</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2994,6 +3089,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123683194</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3124,6 +3224,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123684013</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3258,6 +3363,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123940487</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3383,6 +3493,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125218082</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3512,6 +3627,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127114518</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3646,6 +3766,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132673416</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3774,6 +3899,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111456176</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3908,6 +4038,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112201533</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4024,6 +4159,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134036823</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4151,6 +4291,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134401414</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4275,6 +4420,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111456940</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4404,6 +4554,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112201777</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4529,6 +4684,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124951111</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4667,6 +4827,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125438214</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4791,6 +4956,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437962</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4925,6 +5095,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112201861</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5035,6 +5210,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83575175</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5145,6 +5325,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83575456</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5255,6 +5440,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83576712</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5365,6 +5555,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83576786</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5475,6 +5670,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83577225</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5585,8 +5785,55 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83605368</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>